--- a/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.3334_cdiac_ornlsfa.010/10.3334_cdiac_ornlsfa.010_soil_Carbon__Dissolved_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.3334_cdiac_ornlsfa.010/10.3334_cdiac_ornlsfa.010_soil_Carbon__Dissolved_organic_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1:20</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -584,12 +584,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2:25</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -638,12 +638,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3:29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -692,12 +692,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>3:49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1:53</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>2:61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>3:216</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1:217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -962,12 +962,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2:218</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>3:241</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1:244</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2:250</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>3:418</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1:419</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>2:429</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>1:449</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>3:452</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>2:463</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1:617</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>2:618</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>3:621</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>1:642</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>3:649</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>2:651</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2:17</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1:18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3:21</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1:52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2:60</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>3:62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>1:213</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>3:215</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2:221</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>1:246</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>3:252</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>2:254</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>2:422</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>3:424</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>1:432</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>1:455</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>3:457</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>2:461</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>2:612</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>1:620</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>3:623</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>2:645</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>3:646</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1:652</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1:27</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2:28</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3:31</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2:54</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1:59</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3:63</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>3:211</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>1:219</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>2:223</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>3:243</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2:245</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>1:247</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>2:420</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>1:421</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>3:428</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3932,12 +3932,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>3:450</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>1:451</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>2:453</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>1:610</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>2:611</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>3:624</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>1:643</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>2:644</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>3:656</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>3:104</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1:108</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4526,12 +4526,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>2:121</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1:178</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>2:182</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>3:184</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>2:312</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1:313</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>3:314</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>3:366</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1:372</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -5012,12 +5012,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>2:377</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>2:510</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>3:519</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>1:527</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -5228,12 +5228,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>3:566</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>2:571</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>1:579</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>2:706</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1:718</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -5498,12 +5498,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>3:719</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>3:754</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>2:770</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>1:779</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>2:116</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>1:118</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>3:119</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>2:162</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1:167</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>3:172</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>3:293</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>1:305</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>2:307</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1:358</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>3:365</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>2:367</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6362,12 +6362,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>2:506</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -6416,12 +6416,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>3:518</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -6470,12 +6470,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>1:524</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1:564</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>3:574</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>2:581</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>3:691</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6740,12 +6740,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>1:703</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>2:716</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1:768</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>3:781</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6956,12 +6956,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>2:782</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>3:107</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>2:109</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1:113</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>3:170</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1:171</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -7280,12 +7280,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>2:183</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>3:297</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -7388,12 +7388,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>1:301</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>2:311</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>3:362</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1:370</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2:375</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>2:511</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -7712,12 +7712,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>3:514</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1:526</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -7820,12 +7820,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>3:562</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>1:565</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -7928,12 +7928,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>2:573</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>2:701</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>3:710</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -8090,12 +8090,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>1:717</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1:769</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>3:776</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>2:783</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>2:103</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -8360,12 +8360,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>3:105</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1:106</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1:166</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -8522,12 +8522,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>2:175</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>3:189</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>2:289</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>1:298</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>3:316</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -8792,12 +8792,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1:353</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>3:371</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -8900,12 +8900,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2:378</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>3:504</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -9008,12 +9008,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>1:507</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -9062,12 +9062,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>2:525</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -9116,12 +9116,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>1:567</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -9170,12 +9170,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>2:568</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>3:589</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>2:693</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>1:713</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -9386,12 +9386,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3:715</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>3:771</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>2:774</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -9548,12 +9548,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>1:784</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3:117</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -9656,12 +9656,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1:123</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2:125</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>2:168</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>3:169</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -9872,12 +9872,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1:173</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>2:302</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>3:308</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1:319</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -10088,12 +10088,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1:355</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -10142,12 +10142,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>3:364</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -10196,12 +10196,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>2:376</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -10250,12 +10250,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>2:499</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>3:517</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -10358,12 +10358,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>1:523</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>2:577</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1:588</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -10520,12 +10520,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>3:591</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>2:683</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>1:704</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -10682,12 +10682,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>3:711</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>3:759</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -10790,12 +10790,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1:761</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -10844,12 +10844,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>2:775</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
